--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92542813759</v>
+        <v>46157.93118569818</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93118569818</v>
+        <v>46157.93370272173</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93370272173</v>
+        <v>46157.93674953367</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93674953367</v>
+        <v>46158.28196257322</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28196257322</v>
+        <v>46158.29721047047</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29721047047</v>
+        <v>46158.29793025971</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29793025971</v>
+        <v>46158.3335770509</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3335770509</v>
+        <v>46158.37211950267</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37211950267</v>
+        <v>46158.3726884491</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
